--- a/Configs/GameConfig/Datas/reward.xlsx
+++ b/Configs/GameConfig/Datas/reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31335" windowHeight="15570"/>
+    <workbookView windowWidth="18420" windowHeight="13410"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -110,6 +110,24 @@
   </si>
   <si>
     <t>1,1,50|1,2,30</t>
+  </si>
+  <si>
+    <t>推关宝箱1</t>
+  </si>
+  <si>
+    <t>1,1,60|1,2,40</t>
+  </si>
+  <si>
+    <t>推关宝箱2</t>
+  </si>
+  <si>
+    <t>1,1,80|1,2,50</t>
+  </si>
+  <si>
+    <t>推关宝箱3</t>
+  </si>
+  <si>
+    <t>1,1,100|1,2,60</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1087,7 @@
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="3" max="3" width="13.375" customWidth="1"/>
     <col min="4" max="4" width="29.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1222,6 +1240,39 @@
         <v>14</v>
       </c>
     </row>
+    <row r="7" spans="1:20">
+      <c r="B7">
+        <v>2001</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="B8">
+        <v>2002</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="B9">
+        <v>2003</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="11" spans="1:20">
       <c r="C11" s="5"/>
     </row>

--- a/Configs/GameConfig/Datas/reward.xlsx
+++ b/Configs/GameConfig/Datas/reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18420" windowHeight="13410"/>
+    <workbookView windowWidth="17145" windowHeight="14955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -128,6 +128,15 @@
   </si>
   <si>
     <t>1,1,100|1,2,60</t>
+  </si>
+  <si>
+    <t>推关宝箱4</t>
+  </si>
+  <si>
+    <t>推关宝箱5</t>
+  </si>
+  <si>
+    <t>推关宝箱6</t>
   </si>
 </sst>
 </file>
@@ -1273,8 +1282,38 @@
         <v>20</v>
       </c>
     </row>
+    <row r="10" spans="1:20">
+      <c r="B10">
+        <v>2004</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="11" spans="1:20">
-      <c r="C11" s="5"/>
+      <c r="B11">
+        <v>2005</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="B12">
+        <v>2006</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="C13" s="5"/>

--- a/Configs/GameConfig/Datas/reward.xlsx
+++ b/Configs/GameConfig/Datas/reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17145" windowHeight="14955"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -137,6 +137,18 @@
   </si>
   <si>
     <t>推关宝箱6</t>
+  </si>
+  <si>
+    <t>广告礼包1</t>
+  </si>
+  <si>
+    <t>1,1,30|1,2,50</t>
+  </si>
+  <si>
+    <t>广告礼包2</t>
+  </si>
+  <si>
+    <t>1,1,50|1,2,80</t>
   </si>
 </sst>
 </file>
@@ -1316,12 +1328,26 @@
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="B13">
+        <v>3001</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14">
+        <v>3002</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="C15" s="5"/>
